--- a/daily_status.xlsx
+++ b/daily_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,15 +429,20 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Work Done</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Blockers</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
@@ -446,29 +451,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Test Employee</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Web Development Project</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Completed frontend tasks</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Waiting for API</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Will finish backend tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>John Doe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mobile App Project</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Fixed login bugs</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Database issues</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Implement user profile tomorrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>S. Abishek Kumar</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sql done
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SDT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frontend, backend
 </t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">waiting for backend
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">none
 </t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>deploy</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>anto</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>health monitoring sys</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frontend
+</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backed
+</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>none</t>
         </is>
       </c>
     </row>

--- a/daily_status.xlsx
+++ b/daily_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,6 +546,40 @@
         </is>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S. Abishek Kumar</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SDT</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-
+</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-
+</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/daily_status.xlsx
+++ b/daily_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,125 +461,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SDT</t>
+          <t>health monitoring sys</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frontend
-</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">none 
-</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sanjay</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SDT</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend
-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">none
-</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">none
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>S. Abishek Kumar</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>health monitoring sys</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">backend done
-</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">none
-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>S. Abishek Kumar</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SDT</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">-
 </t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">-
 </t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/daily_status.xlsx
+++ b/daily_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,75 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S. Abishek Kumar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>health monitoring sys</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-
+</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-
+</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>S. Abishek Kumar</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SDT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-
+</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-
+</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/daily_status.xlsx
+++ b/daily_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,6 +585,210 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S. Abishek Kumar</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SDT</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Designed the login page UI and navigation bar.
+</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> None.
+</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Start implementing the employee dashboard layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>darika</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SDT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done: Created database schema and connected backend to MySQL.
+</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocker: Minor issue with API response delay.
+</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plan: Complete API testing and optimize response time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ANTO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AI CHATBOX</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done: Cleaned and preprocessed training dataset.
+</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocker: Dataset contains inconsistent labels.
+</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Plan: Fix dataset issues and start model training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SARAVANA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MOBILE FITNESS APP</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done: Designed login screen and implemented UI components.
+</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocker: None.
+</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Plan: Develop user profile page and authentication system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRITHEEV</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DATA ANALYTIC DASHBOARD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done: Built ETL pipeline for sales data.
+</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocker: Data inconsistency from external source.
+</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Plan: Clean data and continue dashboard visualization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ragul</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SDT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Completed data preprocessing and feature selection.
+</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blocker: Model accuracy is low.
+</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Plan: Improve model parameters and retrain.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/daily_status.xlsx
+++ b/daily_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,40 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S. Abishek Kumar</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SDT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">completed front end
+</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waiting for backend 
+</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>deployment</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
